--- a/tests/fixtures/expenses/isracard_minimal.xlsx
+++ b/tests/fixtures/expenses/isracard_minimal.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>₪ 250.00</t>
+          <t>₪ 163.08</t>
         </is>
       </c>
     </row>
